--- a/Tabellen/Hydrotherapie-Kneipp-Guss-Indikation & Kontraindikation.xlsx
+++ b/Tabellen/Hydrotherapie-Kneipp-Guss-Indikation & Kontraindikation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -31,10 +31,13 @@
     <t xml:space="preserve">Kontraindikation </t>
   </si>
   <si>
-    <t xml:space="preserve">Funktion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innervation</t>
+    <t xml:space="preserve">Nenne jeweils 5 Indikationen und Kontraindikationen für eine Hydrotherapie Behandlung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erkrankungen des Bewegungsapparates; neurologische Erkrankungen; internistische Erkrankungen im Früh- / Anfangsstadium; nicht ansteckbare Hauterkrankungen; Atemwegsprobleme; leichte Kreislaufbeschwerden; Erschöpfungssyndrom; Abwehrschwäche; Arthritis; Schmerzen im Bewegungsapparat; Kopfschmerzen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spätstadium Herz-Lungenerkrankung; Blasen-/Nierenentzündungen; Frische Bein- &amp; Beckenvenen Thrombosen (&lt; 4 Wochen); Aneurysmen; frische Operationen; Leberzirrhose; Haut- /Nagelpilz; stark blutende Hämorrhoiden; Infektionskrankheiten; Offene Wunden</t>
   </si>
 </sst>
 </file>
@@ -117,7 +120,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -128,6 +131,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -330,7 +337,7 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="84.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="32.45"/>
@@ -348,36 +355,37 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
       <c r="C3" s="3"/>
-      <c r="E3" s="4"/>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="E4" s="4"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="E4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="E5" s="4"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="E5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3"/>
+      <c r="B6" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
